--- a/TCAM_solver_data.xlsx
+++ b/TCAM_solver_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kyleswartz\projects\ETtoKGT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E4A52E5-8CC5-47DC-9F9E-C4576E0A9E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C9D118-93F1-47D5-A2AC-CCB981D36289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{369FE082-AEFE-4142-B79C-87070DFA0112}"/>
+    <workbookView xWindow="2508" yWindow="2508" windowWidth="17280" windowHeight="10932" xr2:uid="{369FE082-AEFE-4142-B79C-87070DFA0112}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="16">
   <si>
     <t>Alloy</t>
   </si>
@@ -59,21 +59,6 @@
     <t>Hf2Mo2Ta48W48 (at%)</t>
   </si>
   <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>Hf2Nb4Ta46W48 (at%)</t>
-  </si>
-  <si>
     <t>W</t>
   </si>
   <si>
@@ -93,6 +78,15 @@
   </si>
   <si>
     <t>V</t>
+  </si>
+  <si>
+    <t>LED (J/m)</t>
+  </si>
+  <si>
+    <t>Velocity (mm/s)</t>
+  </si>
+  <si>
+    <t>Mo5Nb55Ta5W35 (at%)</t>
   </si>
 </sst>
 </file>
@@ -122,7 +116,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -135,8 +129,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -144,11 +144,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2"/>
+      </left>
+      <right style="thin">
+        <color theme="2"/>
+      </right>
+      <top style="thin">
+        <color theme="2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -159,10 +174,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -499,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4880C6CB-5E4F-4D6F-8B2F-CAB39A7F9F86}">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5546875" style="3" customWidth="1"/>
@@ -512,12 +530,12 @@
     <col min="8" max="8" width="5.44140625" style="3" customWidth="1"/>
     <col min="9" max="9" width="6.77734375" style="3" customWidth="1"/>
     <col min="10" max="10" width="8.88671875" style="3"/>
-    <col min="11" max="11" width="13.109375" style="3" customWidth="1"/>
-    <col min="12" max="12" width="12.21875" style="3" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="3"/>
+    <col min="11" max="13" width="13.109375" style="3" customWidth="1"/>
+    <col min="14" max="14" width="12.21875" style="3" customWidth="1"/>
+    <col min="15" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -525,25 +543,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>17</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>2</v>
@@ -552,350 +570,746 @@
         <v>3</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="D2" s="5">
-        <v>0</v>
-      </c>
-      <c r="E2" s="5">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="G2" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="H2" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="I2" s="5">
+      <c r="C2" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I2" s="3">
         <v>0</v>
       </c>
       <c r="J2" s="3">
+        <v>50</v>
+      </c>
+      <c r="K2" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="L2" s="3">
+        <f t="shared" ref="L2:L18" si="0">K2*1000</f>
+        <v>100</v>
+      </c>
+      <c r="M2" s="3">
+        <f t="shared" ref="M2:M9" si="1">J2/K2</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>50</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="L3" s="3">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="M3" s="3">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>0</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3">
+        <v>50</v>
+      </c>
+      <c r="K4" s="3">
+        <v>1</v>
+      </c>
+      <c r="L4" s="3">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="M4" s="3">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>0</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>50</v>
+      </c>
+      <c r="K5" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L5" s="3">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="M5" s="3">
+        <f t="shared" si="1"/>
+        <v>33.333333333333336</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3">
+        <v>150</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="L6" s="3">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="M6" s="3">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3">
+        <v>150</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="L7" s="3">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="M7" s="3">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>150</v>
+      </c>
+      <c r="K8" s="3">
+        <v>1</v>
+      </c>
+      <c r="L8" s="3">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="M8" s="3">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>150</v>
+      </c>
+      <c r="K9" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L9" s="3">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="M9" s="3">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
         <v>250</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K10" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="3">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="M10" s="3">
+        <f t="shared" ref="M10:M15" si="2">J10/K10</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>0</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3">
+        <v>250</v>
+      </c>
+      <c r="K11" s="3">
         <v>0.5</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>0</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="D3" s="5">
-        <v>0</v>
-      </c>
-      <c r="E3" s="5">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3">
-        <v>200</v>
-      </c>
-      <c r="K3" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>0</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="D4" s="5">
-        <v>0</v>
-      </c>
-      <c r="E4" s="5">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3">
+      <c r="L11" s="3">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="M11" s="3">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>0</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
         <v>250</v>
       </c>
-      <c r="K4" s="3">
-        <v>1.25</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>0</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="D5" s="5">
-        <v>0</v>
-      </c>
-      <c r="E5" s="5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3">
-        <v>125</v>
-      </c>
-      <c r="K5" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
-        <v>0</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="D6" s="5">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="G6" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="H6" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3">
-        <v>275</v>
-      </c>
-      <c r="K6" s="3">
-        <v>1.65</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="D7" s="5">
-        <v>0</v>
-      </c>
-      <c r="E7" s="5">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="H7" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3">
-        <v>305</v>
-      </c>
-      <c r="K7" s="3">
+      <c r="K12" s="3">
         <v>1</v>
       </c>
-      <c r="L7" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="D8" s="5">
-        <v>0</v>
-      </c>
-      <c r="E8" s="5">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="H8" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="I8" s="5">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="L12" s="3">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="M12" s="3">
+        <f t="shared" si="2"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>0</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3">
+        <v>250</v>
+      </c>
+      <c r="K13" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L13" s="3">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="M13" s="3">
+        <f t="shared" si="2"/>
+        <v>166.66666666666666</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>0</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>350</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="L14" s="3">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="M14" s="3">
+        <f t="shared" si="2"/>
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>0</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>350</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="L15" s="3">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="M15" s="3">
+        <f t="shared" si="2"/>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>0</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3">
+        <v>350</v>
+      </c>
+      <c r="K16" s="3">
+        <v>1</v>
+      </c>
+      <c r="L16" s="3">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="M16" s="3">
+        <f t="shared" ref="M16:M18" si="3">J16/K16</f>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>0</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
+        <v>350</v>
+      </c>
+      <c r="K17" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L17" s="3">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="M17" s="3">
+        <f t="shared" si="3"/>
+        <v>233.33333333333334</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <v>19</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.35</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F18" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="H18" s="5">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
         <v>300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K18" s="5">
         <v>0.3</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="D9" s="5">
-        <v>0</v>
-      </c>
-      <c r="E9" s="5">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="H9" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="I9" s="5">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3">
-        <v>250</v>
-      </c>
-      <c r="K9" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
-        <v>13</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="3">
-        <v>0.48</v>
-      </c>
-      <c r="D10" s="3">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0.04</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0.46</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3">
-        <v>260</v>
-      </c>
-      <c r="K10" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="L18" s="5">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="M18" s="5">
+        <f t="shared" si="3"/>
+        <v>1000</v>
+      </c>
+      <c r="T18" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
